--- a/testing/AvantisChannelListTesting.xlsx
+++ b/testing/AvantisChannelListTesting.xlsx
@@ -2038,20 +2038,22 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="35" min="35" style="2" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="37" style="2" width="4.29"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="60" min="53" style="2" width="4.29"/>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="61" min="61" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="69" min="62" style="2" width="4.29"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="61" min="61" style="3" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="69" min="62" style="2" width="4.29"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="70" min="70" style="3" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="94" min="71" style="2" width="4.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="86" min="71" style="2" width="4.29"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="94" min="87" style="2" width="4.29"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="95" min="95" style="2" width="11"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="103" min="96" style="2" width="4.29"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="107" min="104" style="2" width="3.56"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="108" min="108" style="2" width="10.42"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="116" min="109" style="2" width="4.29"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="120" min="117" style="2" width="3.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="121" min="121" style="3" width="35.84"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="135" min="122" style="2" width="11"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="144" min="137" style="2" width="10.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16377" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="121" min="121" style="2" width="12.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="122" min="122" style="3" width="35.84"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="136" min="123" style="2" width="11"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="145" min="138" style="2" width="10.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16378" style="3" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" s="10" customFormat="true" ht="75.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2436,10 +2438,10 @@
       <c r="DP1" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="DQ1" s="10" t="s">
+      <c r="DQ1" s="8"/>
+      <c r="DR1" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="DR1" s="8"/>
       <c r="DS1" s="8"/>
       <c r="DT1" s="8"/>
       <c r="DU1" s="8"/>
@@ -2453,7 +2455,7 @@
       <c r="EC1" s="8"/>
       <c r="ED1" s="8"/>
       <c r="EE1" s="8"/>
-      <c r="EG1" s="8"/>
+      <c r="EF1" s="8"/>
       <c r="EH1" s="8"/>
       <c r="EI1" s="8"/>
       <c r="EJ1" s="8"/>
@@ -2461,7 +2463,7 @@
       <c r="EL1" s="8"/>
       <c r="EM1" s="8"/>
       <c r="EN1" s="8"/>
-      <c r="EO1" s="3"/>
+      <c r="EO1" s="8"/>
       <c r="EP1" s="3"/>
       <c r="EQ1" s="3"/>
       <c r="ER1" s="3"/>
@@ -2479,14 +2481,14 @@
       <c r="FD1" s="3"/>
       <c r="FE1" s="3"/>
       <c r="FF1" s="3"/>
-      <c r="XEW1" s="0"/>
-      <c r="XEX1" s="0"/>
-      <c r="XEY1" s="0"/>
-      <c r="XEZ1" s="0"/>
-      <c r="XFA1" s="0"/>
-      <c r="XFB1" s="0"/>
-      <c r="XFC1" s="0"/>
-      <c r="XFD1" s="0"/>
+      <c r="FG1" s="3"/>
+      <c r="XEX1" s="3"/>
+      <c r="XEY1" s="3"/>
+      <c r="XEZ1" s="3"/>
+      <c r="XFA1" s="3"/>
+      <c r="XFB1" s="3"/>
+      <c r="XFC1" s="3"/>
+      <c r="XFD1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
@@ -2805,7 +2807,6 @@
       <c r="DP2" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG2" s="11"/>
       <c r="EH2" s="11"/>
       <c r="EI2" s="11"/>
       <c r="EJ2" s="11"/>
@@ -2813,6 +2814,7 @@
       <c r="EL2" s="11"/>
       <c r="EM2" s="11"/>
       <c r="EN2" s="11"/>
+      <c r="EO2" s="11"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
@@ -3131,7 +3133,6 @@
       <c r="DP3" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG3" s="11"/>
       <c r="EH3" s="11"/>
       <c r="EI3" s="11"/>
       <c r="EJ3" s="11"/>
@@ -3139,6 +3140,7 @@
       <c r="EL3" s="11"/>
       <c r="EM3" s="11"/>
       <c r="EN3" s="11"/>
+      <c r="EO3" s="11"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
@@ -3459,7 +3461,6 @@
       <c r="DP4" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG4" s="11"/>
       <c r="EH4" s="11"/>
       <c r="EI4" s="11"/>
       <c r="EJ4" s="11"/>
@@ -3467,6 +3468,7 @@
       <c r="EL4" s="11"/>
       <c r="EM4" s="11"/>
       <c r="EN4" s="11"/>
+      <c r="EO4" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
@@ -3785,7 +3787,6 @@
       <c r="DP5" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG5" s="11"/>
       <c r="EH5" s="11"/>
       <c r="EI5" s="11"/>
       <c r="EJ5" s="11"/>
@@ -3793,6 +3794,7 @@
       <c r="EL5" s="11"/>
       <c r="EM5" s="11"/>
       <c r="EN5" s="11"/>
+      <c r="EO5" s="11"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
@@ -4113,7 +4115,6 @@
       <c r="DP6" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG6" s="11"/>
       <c r="EH6" s="11"/>
       <c r="EI6" s="11"/>
       <c r="EJ6" s="11"/>
@@ -4121,6 +4122,7 @@
       <c r="EL6" s="11"/>
       <c r="EM6" s="11"/>
       <c r="EN6" s="11"/>
+      <c r="EO6" s="11"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
@@ -4439,7 +4441,6 @@
       <c r="DP7" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG7" s="11"/>
       <c r="EH7" s="11"/>
       <c r="EI7" s="11"/>
       <c r="EJ7" s="11"/>
@@ -4447,6 +4448,7 @@
       <c r="EL7" s="11"/>
       <c r="EM7" s="11"/>
       <c r="EN7" s="11"/>
+      <c r="EO7" s="11"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
@@ -4767,7 +4769,6 @@
       <c r="DP8" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG8" s="11"/>
       <c r="EH8" s="11"/>
       <c r="EI8" s="11"/>
       <c r="EJ8" s="11"/>
@@ -4775,6 +4776,7 @@
       <c r="EL8" s="11"/>
       <c r="EM8" s="11"/>
       <c r="EN8" s="11"/>
+      <c r="EO8" s="11"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
@@ -5093,7 +5095,6 @@
       <c r="DP9" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG9" s="11"/>
       <c r="EH9" s="11"/>
       <c r="EI9" s="11"/>
       <c r="EJ9" s="11"/>
@@ -5101,6 +5102,7 @@
       <c r="EL9" s="11"/>
       <c r="EM9" s="11"/>
       <c r="EN9" s="11"/>
+      <c r="EO9" s="11"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
@@ -5435,7 +5437,6 @@
       <c r="DP10" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG10" s="11"/>
       <c r="EH10" s="11"/>
       <c r="EI10" s="11"/>
       <c r="EJ10" s="11"/>
@@ -5443,6 +5444,7 @@
       <c r="EL10" s="11"/>
       <c r="EM10" s="11"/>
       <c r="EN10" s="11"/>
+      <c r="EO10" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
@@ -5775,7 +5777,6 @@
       <c r="DP11" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG11" s="11"/>
       <c r="EH11" s="11"/>
       <c r="EI11" s="11"/>
       <c r="EJ11" s="11"/>
@@ -5783,6 +5784,7 @@
       <c r="EL11" s="11"/>
       <c r="EM11" s="11"/>
       <c r="EN11" s="11"/>
+      <c r="EO11" s="11"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
@@ -6117,7 +6119,6 @@
       <c r="DP12" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG12" s="11"/>
       <c r="EH12" s="11"/>
       <c r="EI12" s="11"/>
       <c r="EJ12" s="11"/>
@@ -6125,6 +6126,7 @@
       <c r="EL12" s="11"/>
       <c r="EM12" s="11"/>
       <c r="EN12" s="11"/>
+      <c r="EO12" s="11"/>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
@@ -6457,7 +6459,6 @@
       <c r="DP13" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG13" s="11"/>
       <c r="EH13" s="11"/>
       <c r="EI13" s="11"/>
       <c r="EJ13" s="11"/>
@@ -6465,6 +6466,7 @@
       <c r="EL13" s="11"/>
       <c r="EM13" s="11"/>
       <c r="EN13" s="11"/>
+      <c r="EO13" s="11"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
@@ -6779,7 +6781,6 @@
       <c r="DP14" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG14" s="11"/>
       <c r="EH14" s="11"/>
       <c r="EI14" s="11"/>
       <c r="EJ14" s="11"/>
@@ -6787,6 +6788,7 @@
       <c r="EL14" s="11"/>
       <c r="EM14" s="11"/>
       <c r="EN14" s="11"/>
+      <c r="EO14" s="11"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
@@ -7107,7 +7109,6 @@
       <c r="DP15" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG15" s="11"/>
       <c r="EH15" s="11"/>
       <c r="EI15" s="11"/>
       <c r="EJ15" s="11"/>
@@ -7115,6 +7116,7 @@
       <c r="EL15" s="11"/>
       <c r="EM15" s="11"/>
       <c r="EN15" s="11"/>
+      <c r="EO15" s="11"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
@@ -7435,7 +7437,6 @@
       <c r="DP16" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG16" s="11"/>
       <c r="EH16" s="11"/>
       <c r="EI16" s="11"/>
       <c r="EJ16" s="11"/>
@@ -7443,6 +7444,7 @@
       <c r="EL16" s="11"/>
       <c r="EM16" s="11"/>
       <c r="EN16" s="11"/>
+      <c r="EO16" s="11"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
@@ -7763,7 +7765,6 @@
       <c r="DP17" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG17" s="11"/>
       <c r="EH17" s="11"/>
       <c r="EI17" s="11"/>
       <c r="EJ17" s="11"/>
@@ -7771,6 +7772,7 @@
       <c r="EL17" s="11"/>
       <c r="EM17" s="11"/>
       <c r="EN17" s="11"/>
+      <c r="EO17" s="11"/>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
@@ -8091,7 +8093,6 @@
       <c r="DP18" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG18" s="11"/>
       <c r="EH18" s="11"/>
       <c r="EI18" s="11"/>
       <c r="EJ18" s="11"/>
@@ -8099,6 +8100,7 @@
       <c r="EL18" s="11"/>
       <c r="EM18" s="11"/>
       <c r="EN18" s="11"/>
+      <c r="EO18" s="11"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
@@ -8419,7 +8421,6 @@
       <c r="DP19" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG19" s="11"/>
       <c r="EH19" s="11"/>
       <c r="EI19" s="11"/>
       <c r="EJ19" s="11"/>
@@ -8427,6 +8428,7 @@
       <c r="EL19" s="11"/>
       <c r="EM19" s="11"/>
       <c r="EN19" s="11"/>
+      <c r="EO19" s="11"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
@@ -8747,7 +8749,6 @@
       <c r="DP20" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG20" s="11"/>
       <c r="EH20" s="11"/>
       <c r="EI20" s="11"/>
       <c r="EJ20" s="11"/>
@@ -8755,6 +8756,7 @@
       <c r="EL20" s="11"/>
       <c r="EM20" s="11"/>
       <c r="EN20" s="11"/>
+      <c r="EO20" s="11"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
@@ -9075,7 +9077,6 @@
       <c r="DP21" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG21" s="11"/>
       <c r="EH21" s="11"/>
       <c r="EI21" s="11"/>
       <c r="EJ21" s="11"/>
@@ -9083,6 +9084,7 @@
       <c r="EL21" s="11"/>
       <c r="EM21" s="11"/>
       <c r="EN21" s="11"/>
+      <c r="EO21" s="11"/>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="11" t="s">
@@ -9417,7 +9419,6 @@
       <c r="DP22" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG22" s="11"/>
       <c r="EH22" s="11"/>
       <c r="EI22" s="11"/>
       <c r="EJ22" s="11"/>
@@ -9425,6 +9426,7 @@
       <c r="EL22" s="11"/>
       <c r="EM22" s="11"/>
       <c r="EN22" s="11"/>
+      <c r="EO22" s="11"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="11" t="s">
@@ -9759,7 +9761,6 @@
       <c r="DP23" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG23" s="11"/>
       <c r="EH23" s="11"/>
       <c r="EI23" s="11"/>
       <c r="EJ23" s="11"/>
@@ -9767,6 +9768,7 @@
       <c r="EL23" s="11"/>
       <c r="EM23" s="11"/>
       <c r="EN23" s="11"/>
+      <c r="EO23" s="11"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
@@ -10101,7 +10103,6 @@
       <c r="DP24" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG24" s="11"/>
       <c r="EH24" s="11"/>
       <c r="EI24" s="11"/>
       <c r="EJ24" s="11"/>
@@ -10109,6 +10110,7 @@
       <c r="EL24" s="11"/>
       <c r="EM24" s="11"/>
       <c r="EN24" s="11"/>
+      <c r="EO24" s="11"/>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="11" t="s">
@@ -10443,7 +10445,6 @@
       <c r="DP25" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG25" s="11"/>
       <c r="EH25" s="11"/>
       <c r="EI25" s="11"/>
       <c r="EJ25" s="11"/>
@@ -10451,6 +10452,7 @@
       <c r="EL25" s="11"/>
       <c r="EM25" s="11"/>
       <c r="EN25" s="11"/>
+      <c r="EO25" s="11"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="11" t="s">
@@ -10785,7 +10787,6 @@
       <c r="DP26" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG26" s="11"/>
       <c r="EH26" s="11"/>
       <c r="EI26" s="11"/>
       <c r="EJ26" s="11"/>
@@ -10793,6 +10794,7 @@
       <c r="EL26" s="11"/>
       <c r="EM26" s="11"/>
       <c r="EN26" s="11"/>
+      <c r="EO26" s="11"/>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
@@ -11127,7 +11129,6 @@
       <c r="DP27" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG27" s="11"/>
       <c r="EH27" s="11"/>
       <c r="EI27" s="11"/>
       <c r="EJ27" s="11"/>
@@ -11135,6 +11136,7 @@
       <c r="EL27" s="11"/>
       <c r="EM27" s="11"/>
       <c r="EN27" s="11"/>
+      <c r="EO27" s="11"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
@@ -11469,7 +11471,6 @@
       <c r="DP28" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG28" s="11"/>
       <c r="EH28" s="11"/>
       <c r="EI28" s="11"/>
       <c r="EJ28" s="11"/>
@@ -11477,6 +11478,7 @@
       <c r="EL28" s="11"/>
       <c r="EM28" s="11"/>
       <c r="EN28" s="11"/>
+      <c r="EO28" s="11"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="11" t="s">
@@ -11811,7 +11813,6 @@
       <c r="DP29" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG29" s="11"/>
       <c r="EH29" s="11"/>
       <c r="EI29" s="11"/>
       <c r="EJ29" s="11"/>
@@ -11819,6 +11820,7 @@
       <c r="EL29" s="11"/>
       <c r="EM29" s="11"/>
       <c r="EN29" s="11"/>
+      <c r="EO29" s="11"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="11" t="s">
@@ -12153,7 +12155,6 @@
       <c r="DP30" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG30" s="11"/>
       <c r="EH30" s="11"/>
       <c r="EI30" s="11"/>
       <c r="EJ30" s="11"/>
@@ -12161,6 +12162,7 @@
       <c r="EL30" s="11"/>
       <c r="EM30" s="11"/>
       <c r="EN30" s="11"/>
+      <c r="EO30" s="11"/>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="11" t="s">
@@ -12495,7 +12497,6 @@
       <c r="DP31" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG31" s="11"/>
       <c r="EH31" s="11"/>
       <c r="EI31" s="11"/>
       <c r="EJ31" s="11"/>
@@ -12503,6 +12504,7 @@
       <c r="EL31" s="11"/>
       <c r="EM31" s="11"/>
       <c r="EN31" s="11"/>
+      <c r="EO31" s="11"/>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="11" t="s">
@@ -12837,7 +12839,6 @@
       <c r="DP32" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG32" s="11"/>
       <c r="EH32" s="11"/>
       <c r="EI32" s="11"/>
       <c r="EJ32" s="11"/>
@@ -12845,6 +12846,7 @@
       <c r="EL32" s="11"/>
       <c r="EM32" s="11"/>
       <c r="EN32" s="11"/>
+      <c r="EO32" s="11"/>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
@@ -13179,7 +13181,6 @@
       <c r="DP33" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG33" s="11"/>
       <c r="EH33" s="11"/>
       <c r="EI33" s="11"/>
       <c r="EJ33" s="11"/>
@@ -13187,6 +13188,7 @@
       <c r="EL33" s="11"/>
       <c r="EM33" s="11"/>
       <c r="EN33" s="11"/>
+      <c r="EO33" s="11"/>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
@@ -13521,7 +13523,6 @@
       <c r="DP34" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG34" s="11"/>
       <c r="EH34" s="11"/>
       <c r="EI34" s="11"/>
       <c r="EJ34" s="11"/>
@@ -13529,6 +13530,7 @@
       <c r="EL34" s="11"/>
       <c r="EM34" s="11"/>
       <c r="EN34" s="11"/>
+      <c r="EO34" s="11"/>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
@@ -13863,7 +13865,6 @@
       <c r="DP35" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG35" s="11"/>
       <c r="EH35" s="11"/>
       <c r="EI35" s="11"/>
       <c r="EJ35" s="11"/>
@@ -13871,6 +13872,7 @@
       <c r="EL35" s="11"/>
       <c r="EM35" s="11"/>
       <c r="EN35" s="11"/>
+      <c r="EO35" s="11"/>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
@@ -14205,7 +14207,6 @@
       <c r="DP36" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG36" s="11"/>
       <c r="EH36" s="11"/>
       <c r="EI36" s="11"/>
       <c r="EJ36" s="11"/>
@@ -14213,6 +14214,7 @@
       <c r="EL36" s="11"/>
       <c r="EM36" s="11"/>
       <c r="EN36" s="11"/>
+      <c r="EO36" s="11"/>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
@@ -14547,7 +14549,6 @@
       <c r="DP37" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG37" s="11"/>
       <c r="EH37" s="11"/>
       <c r="EI37" s="11"/>
       <c r="EJ37" s="11"/>
@@ -14555,6 +14556,7 @@
       <c r="EL37" s="11"/>
       <c r="EM37" s="11"/>
       <c r="EN37" s="11"/>
+      <c r="EO37" s="11"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
@@ -14887,7 +14889,6 @@
       <c r="DP38" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG38" s="11"/>
       <c r="EH38" s="11"/>
       <c r="EI38" s="11"/>
       <c r="EJ38" s="11"/>
@@ -14895,6 +14896,7 @@
       <c r="EL38" s="11"/>
       <c r="EM38" s="11"/>
       <c r="EN38" s="11"/>
+      <c r="EO38" s="11"/>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
@@ -15227,7 +15229,6 @@
       <c r="DP39" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG39" s="11"/>
       <c r="EH39" s="11"/>
       <c r="EI39" s="11"/>
       <c r="EJ39" s="11"/>
@@ -15235,6 +15236,7 @@
       <c r="EL39" s="11"/>
       <c r="EM39" s="11"/>
       <c r="EN39" s="11"/>
+      <c r="EO39" s="11"/>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
@@ -15567,7 +15569,6 @@
       <c r="DP40" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG40" s="11"/>
       <c r="EH40" s="11"/>
       <c r="EI40" s="11"/>
       <c r="EJ40" s="11"/>
@@ -15575,6 +15576,7 @@
       <c r="EL40" s="11"/>
       <c r="EM40" s="11"/>
       <c r="EN40" s="11"/>
+      <c r="EO40" s="11"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
@@ -15907,7 +15909,6 @@
       <c r="DP41" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG41" s="11"/>
       <c r="EH41" s="11"/>
       <c r="EI41" s="11"/>
       <c r="EJ41" s="11"/>
@@ -15915,6 +15916,7 @@
       <c r="EL41" s="11"/>
       <c r="EM41" s="11"/>
       <c r="EN41" s="11"/>
+      <c r="EO41" s="11"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11" t="s">
@@ -16247,7 +16249,6 @@
       <c r="DP42" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG42" s="11"/>
       <c r="EH42" s="11"/>
       <c r="EI42" s="11"/>
       <c r="EJ42" s="11"/>
@@ -16255,6 +16256,7 @@
       <c r="EL42" s="11"/>
       <c r="EM42" s="11"/>
       <c r="EN42" s="11"/>
+      <c r="EO42" s="11"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="11" t="s">
@@ -16587,7 +16589,6 @@
       <c r="DP43" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG43" s="11"/>
       <c r="EH43" s="11"/>
       <c r="EI43" s="11"/>
       <c r="EJ43" s="11"/>
@@ -16595,6 +16596,7 @@
       <c r="EL43" s="11"/>
       <c r="EM43" s="11"/>
       <c r="EN43" s="11"/>
+      <c r="EO43" s="11"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="11" t="s">
@@ -16927,7 +16929,6 @@
       <c r="DP44" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG44" s="11"/>
       <c r="EH44" s="11"/>
       <c r="EI44" s="11"/>
       <c r="EJ44" s="11"/>
@@ -16935,6 +16936,7 @@
       <c r="EL44" s="11"/>
       <c r="EM44" s="11"/>
       <c r="EN44" s="11"/>
+      <c r="EO44" s="11"/>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="11" t="s">
@@ -17267,7 +17269,6 @@
       <c r="DP45" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG45" s="11"/>
       <c r="EH45" s="11"/>
       <c r="EI45" s="11"/>
       <c r="EJ45" s="11"/>
@@ -17275,6 +17276,7 @@
       <c r="EL45" s="11"/>
       <c r="EM45" s="11"/>
       <c r="EN45" s="11"/>
+      <c r="EO45" s="11"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
@@ -17607,7 +17609,6 @@
       <c r="DP46" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG46" s="11"/>
       <c r="EH46" s="11"/>
       <c r="EI46" s="11"/>
       <c r="EJ46" s="11"/>
@@ -17615,6 +17616,7 @@
       <c r="EL46" s="11"/>
       <c r="EM46" s="11"/>
       <c r="EN46" s="11"/>
+      <c r="EO46" s="11"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="11" t="s">
@@ -17947,7 +17949,6 @@
       <c r="DP47" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG47" s="11"/>
       <c r="EH47" s="11"/>
       <c r="EI47" s="11"/>
       <c r="EJ47" s="11"/>
@@ -17955,6 +17956,7 @@
       <c r="EL47" s="11"/>
       <c r="EM47" s="11"/>
       <c r="EN47" s="11"/>
+      <c r="EO47" s="11"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
@@ -18287,7 +18289,6 @@
       <c r="DP48" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG48" s="11"/>
       <c r="EH48" s="11"/>
       <c r="EI48" s="11"/>
       <c r="EJ48" s="11"/>
@@ -18295,6 +18296,7 @@
       <c r="EL48" s="11"/>
       <c r="EM48" s="11"/>
       <c r="EN48" s="11"/>
+      <c r="EO48" s="11"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
@@ -18627,7 +18629,6 @@
       <c r="DP49" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG49" s="11"/>
       <c r="EH49" s="11"/>
       <c r="EI49" s="11"/>
       <c r="EJ49" s="11"/>
@@ -18635,6 +18636,7 @@
       <c r="EL49" s="11"/>
       <c r="EM49" s="11"/>
       <c r="EN49" s="11"/>
+      <c r="EO49" s="11"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="11" t="s">
@@ -18969,7 +18971,6 @@
       <c r="DP50" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG50" s="11"/>
       <c r="EH50" s="11"/>
       <c r="EI50" s="11"/>
       <c r="EJ50" s="11"/>
@@ -18977,6 +18978,7 @@
       <c r="EL50" s="11"/>
       <c r="EM50" s="11"/>
       <c r="EN50" s="11"/>
+      <c r="EO50" s="11"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="11" t="s">
@@ -19311,7 +19313,6 @@
       <c r="DP51" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG51" s="11"/>
       <c r="EH51" s="11"/>
       <c r="EI51" s="11"/>
       <c r="EJ51" s="11"/>
@@ -19319,6 +19320,7 @@
       <c r="EL51" s="11"/>
       <c r="EM51" s="11"/>
       <c r="EN51" s="11"/>
+      <c r="EO51" s="11"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="11" t="s">
@@ -19653,7 +19655,6 @@
       <c r="DP52" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG52" s="11"/>
       <c r="EH52" s="11"/>
       <c r="EI52" s="11"/>
       <c r="EJ52" s="11"/>
@@ -19661,6 +19662,7 @@
       <c r="EL52" s="11"/>
       <c r="EM52" s="11"/>
       <c r="EN52" s="11"/>
+      <c r="EO52" s="11"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="11" t="s">
@@ -19995,7 +19997,6 @@
       <c r="DP53" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG53" s="11"/>
       <c r="EH53" s="11"/>
       <c r="EI53" s="11"/>
       <c r="EJ53" s="11"/>
@@ -20003,6 +20004,7 @@
       <c r="EL53" s="11"/>
       <c r="EM53" s="11"/>
       <c r="EN53" s="11"/>
+      <c r="EO53" s="11"/>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="11" t="s">
@@ -20337,7 +20339,6 @@
       <c r="DP54" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG54" s="11"/>
       <c r="EH54" s="11"/>
       <c r="EI54" s="11"/>
       <c r="EJ54" s="11"/>
@@ -20345,6 +20346,7 @@
       <c r="EL54" s="11"/>
       <c r="EM54" s="11"/>
       <c r="EN54" s="11"/>
+      <c r="EO54" s="11"/>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="11" t="s">
@@ -20679,7 +20681,6 @@
       <c r="DP55" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG55" s="11"/>
       <c r="EH55" s="11"/>
       <c r="EI55" s="11"/>
       <c r="EJ55" s="11"/>
@@ -20687,6 +20688,7 @@
       <c r="EL55" s="11"/>
       <c r="EM55" s="11"/>
       <c r="EN55" s="11"/>
+      <c r="EO55" s="11"/>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="11" t="s">
@@ -21021,7 +21023,6 @@
       <c r="DP56" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG56" s="11"/>
       <c r="EH56" s="11"/>
       <c r="EI56" s="11"/>
       <c r="EJ56" s="11"/>
@@ -21029,6 +21030,7 @@
       <c r="EL56" s="11"/>
       <c r="EM56" s="11"/>
       <c r="EN56" s="11"/>
+      <c r="EO56" s="11"/>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="11" t="s">
@@ -21363,7 +21365,6 @@
       <c r="DP57" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG57" s="11"/>
       <c r="EH57" s="11"/>
       <c r="EI57" s="11"/>
       <c r="EJ57" s="11"/>
@@ -21371,6 +21372,7 @@
       <c r="EL57" s="11"/>
       <c r="EM57" s="11"/>
       <c r="EN57" s="11"/>
+      <c r="EO57" s="11"/>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="11" t="s">
@@ -21705,7 +21707,6 @@
       <c r="DP58" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG58" s="11"/>
       <c r="EH58" s="11"/>
       <c r="EI58" s="11"/>
       <c r="EJ58" s="11"/>
@@ -21713,6 +21714,7 @@
       <c r="EL58" s="11"/>
       <c r="EM58" s="11"/>
       <c r="EN58" s="11"/>
+      <c r="EO58" s="11"/>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="11" t="s">
@@ -22045,7 +22047,6 @@
       <c r="DP59" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG59" s="11"/>
       <c r="EH59" s="11"/>
       <c r="EI59" s="11"/>
       <c r="EJ59" s="11"/>
@@ -22053,6 +22054,7 @@
       <c r="EL59" s="11"/>
       <c r="EM59" s="11"/>
       <c r="EN59" s="11"/>
+      <c r="EO59" s="11"/>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="11" t="s">
@@ -22387,7 +22389,6 @@
       <c r="DP60" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG60" s="11"/>
       <c r="EH60" s="11"/>
       <c r="EI60" s="11"/>
       <c r="EJ60" s="11"/>
@@ -22395,6 +22396,7 @@
       <c r="EL60" s="11"/>
       <c r="EM60" s="11"/>
       <c r="EN60" s="11"/>
+      <c r="EO60" s="11"/>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="11" t="s">
@@ -22729,7 +22731,6 @@
       <c r="DP61" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG61" s="11"/>
       <c r="EH61" s="11"/>
       <c r="EI61" s="11"/>
       <c r="EJ61" s="11"/>
@@ -22737,6 +22738,7 @@
       <c r="EL61" s="11"/>
       <c r="EM61" s="11"/>
       <c r="EN61" s="11"/>
+      <c r="EO61" s="11"/>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="11" t="s">
@@ -23071,7 +23073,6 @@
       <c r="DP62" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG62" s="11"/>
       <c r="EH62" s="11"/>
       <c r="EI62" s="11"/>
       <c r="EJ62" s="11"/>
@@ -23079,6 +23080,7 @@
       <c r="EL62" s="11"/>
       <c r="EM62" s="11"/>
       <c r="EN62" s="11"/>
+      <c r="EO62" s="11"/>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="11" t="s">
@@ -23413,7 +23415,6 @@
       <c r="DP63" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG63" s="11"/>
       <c r="EH63" s="11"/>
       <c r="EI63" s="11"/>
       <c r="EJ63" s="11"/>
@@ -23421,6 +23422,7 @@
       <c r="EL63" s="11"/>
       <c r="EM63" s="11"/>
       <c r="EN63" s="11"/>
+      <c r="EO63" s="11"/>
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="11" t="s">
@@ -23755,7 +23757,6 @@
       <c r="DP64" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG64" s="11"/>
       <c r="EH64" s="11"/>
       <c r="EI64" s="11"/>
       <c r="EJ64" s="11"/>
@@ -23763,6 +23764,7 @@
       <c r="EL64" s="11"/>
       <c r="EM64" s="11"/>
       <c r="EN64" s="11"/>
+      <c r="EO64" s="11"/>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="11" t="s">
@@ -24095,7 +24097,6 @@
       <c r="DP65" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="EG65" s="11"/>
       <c r="EH65" s="11"/>
       <c r="EI65" s="11"/>
       <c r="EJ65" s="11"/>
@@ -24103,6 +24104,7 @@
       <c r="EL65" s="11"/>
       <c r="EM65" s="11"/>
       <c r="EN65" s="11"/>
+      <c r="EO65" s="11"/>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="2"/>

--- a/testing/AvantisChannelListTesting.xlsx
+++ b/testing/AvantisChannelListTesting.xlsx
@@ -2039,17 +2039,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="37" style="2" width="4.29"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="60" min="53" style="2" width="4.29"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="61" min="61" style="3" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="69" min="62" style="2" width="4.29"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="70" min="70" style="3" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="86" min="71" style="2" width="4.29"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="94" min="87" style="2" width="4.29"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="69" min="62" style="2" width="4.29"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="70" min="70" style="3" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="94" min="71" style="2" width="4.29"/>
     <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="95" min="95" style="2" width="11"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="103" min="96" style="2" width="4.29"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="107" min="104" style="2" width="3.56"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="108" min="108" style="2" width="10.42"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="116" min="109" style="2" width="4.29"/>
     <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="120" min="117" style="2" width="3.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="121" min="121" style="2" width="12.01"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="121" min="121" style="2" width="12.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="122" min="122" style="3" width="35.84"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="136" min="123" style="2" width="11"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="145" min="138" style="2" width="10.98"/>
